--- a/src/results/human/human_results_for_presentation.xlsx
+++ b/src/results/human/human_results_for_presentation.xlsx
@@ -8,25 +8,37 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\human\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD66748-D211-4FB1-B775-A94067A948E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965EED26-06FB-4A40-B5F1-4B958FD99802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Original" sheetId="1" r:id="rId1"/>
     <sheet name="Transformed" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="33">
   <si>
     <t>Question</t>
   </si>
@@ -125,9 +137,6 @@
   </si>
   <si>
     <t>Language</t>
-  </si>
-  <si>
-    <t>?</t>
   </si>
 </sst>
 </file>
@@ -808,7 +817,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -3439,7 +3447,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FC88B4-BAD5-4224-8F8B-E42023CF87E4}">
-  <dimension ref="A1:Y48"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="3" customWidth="1"/>
@@ -4811,12 +4819,6 @@
       <c r="G30" s="5">
         <v>0.75433650914135697</v>
       </c>
-      <c r="K30" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="O30"/>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.25">
@@ -4841,12 +4843,6 @@
       <c r="G31" s="5">
         <v>0.69410473022319796</v>
       </c>
-      <c r="K31" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="O31"/>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.25">
@@ -4871,12 +4867,6 @@
       <c r="G32" s="5">
         <v>0.59314412363964997</v>
       </c>
-      <c r="K32" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="O32"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -4901,12 +4891,6 @@
       <c r="G33" s="5">
         <v>0.29080080483815601</v>
       </c>
-      <c r="K33" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="O33"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -4931,12 +4915,6 @@
       <c r="G34" s="5">
         <v>0.40883815970729898</v>
       </c>
-      <c r="K34" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
@@ -4960,12 +4938,6 @@
       <c r="G35" s="5">
         <v>0.95831484749990903</v>
       </c>
-      <c r="K35" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -4989,12 +4961,6 @@
       <c r="G36" s="5">
         <v>1</v>
       </c>
-      <c r="K36" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
@@ -5018,12 +4984,6 @@
       <c r="G37" s="5">
         <v>0.32287320150037802</v>
       </c>
-      <c r="K37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
@@ -5047,12 +5007,6 @@
       <c r="G38" s="5">
         <v>0.92717264994552995</v>
       </c>
-      <c r="K38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
@@ -5076,12 +5030,6 @@
       <c r="G39" s="5">
         <v>0.87070707070706999</v>
       </c>
-      <c r="K39" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
@@ -5105,15 +5053,6 @@
       <c r="G40" s="5">
         <v>0.50213950485175096</v>
       </c>
-      <c r="K40" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
@@ -5137,12 +5076,6 @@
       <c r="G41" s="5">
         <v>0.41656576663693501</v>
       </c>
-      <c r="K41" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -5166,12 +5099,6 @@
       <c r="G42" s="5">
         <v>0.88662628383626696</v>
       </c>
-      <c r="K42" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
@@ -5195,12 +5122,6 @@
       <c r="G43" s="5">
         <v>0.88662628383626696</v>
       </c>
-      <c r="K43" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
@@ -5224,12 +5145,6 @@
       <c r="G44" s="5">
         <v>0.84270097160038404</v>
       </c>
-      <c r="K44" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>32</v>
-      </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
@@ -5252,36 +5167,6 @@
       </c>
       <c r="G45" s="5">
         <v>0.65141719549690702</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K46" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="K48" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -5290,12 +5175,12 @@
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A24:G24"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:O1048576">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="A1:O29 A49:O1048576 A30:J48 M30:O48">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
+        <cfvo type="num" val="0"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="1"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5311,11 +5196,11 @@
         <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="num" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="num" val="1"/>
+        <cfvo type="max"/>
         <color rgb="FFF8696B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FF63BE7B"/>
@@ -5337,4 +5222,202 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE05FBB1-52FD-4982-866C-272CD8759DE0}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:B19">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="1"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="num" val="100"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/results/human/human_results_for_presentation.xlsx
+++ b/src/results/human/human_results_for_presentation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\human\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{965EED26-06FB-4A40-B5F1-4B958FD99802}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC3066B-6B67-43D0-BE0A-7F2333FE9E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="43">
   <si>
     <t>Question</t>
   </si>
@@ -137,6 +137,36 @@
   </si>
   <si>
     <t>Language</t>
+  </si>
+  <si>
+    <t>Averaged</t>
+  </si>
+  <si>
+    <t>human1 vs human2</t>
+  </si>
+  <si>
+    <t>human1 vs human3</t>
+  </si>
+  <si>
+    <t>human2 vs human3</t>
+  </si>
+  <si>
+    <t>Pozitīva precizitāte</t>
+  </si>
+  <si>
+    <t>Pozitīvs pārklājums</t>
+  </si>
+  <si>
+    <t>Pozitīvs F1</t>
+  </si>
+  <si>
+    <t>Makro F1</t>
+  </si>
+  <si>
+    <t>Koena kappa</t>
+  </si>
+  <si>
+    <t>Metjūsa korelācijas koeficients</t>
   </si>
 </sst>
 </file>
@@ -1131,7 +1161,513 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Transformed!$A$50</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>human1 vs human2</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Transformed!$B$49:$G$49</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Pozitīva precizitāte</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pozitīvs pārklājums</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pozitīvs F1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Makro F1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Koena kappa</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Metjūsa korelācijas koeficients</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Transformed!$B$50:$G$50</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.90701754385964894</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.71016483516483497</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.79661016949152497</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.78190296834364603</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57108042242079604</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.59088045011143397</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DC94-4D9A-9598-A696E0D9D3DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Transformed!$A$51</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>human1 vs human3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Transformed!$B$49:$G$49</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Pozitīva precizitāte</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pozitīvs pārklājums</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pozitīvs F1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Makro F1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Koena kappa</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Metjūsa korelācijas koeficients</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Transformed!$B$51:$G$51</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.82832080200501201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.90796703296703296</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.86631716906946199</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.820575803077777</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.64241893076248902</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.64731008158916303</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DC94-4D9A-9598-A696E0D9D3DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Transformed!$A$52</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>human2 vs human3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Transformed!$B$49:$G$49</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Pozitīva precizitāte</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Pozitīvs pārklājums</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Pozitīvs F1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Makro F1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Koena kappa</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Metjūsa korelācijas koeficients</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Transformed!$B$52:$G$52</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>0.66165413533834505</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.92631578947368398</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.77192982456140302</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.73934837092731798</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.49667271627344201</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.53411494579609897</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DC94-4D9A-9598-A696E0D9D3DD}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1779213343"/>
+        <c:axId val="1779211903"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1779213343"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1779211903"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1779211903"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1779213343"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1674,6 +2210,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1707,6 +2746,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>685800</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>138112</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1114425</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB296B05-9041-3786-685E-9A553B8CA552}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3447,7 +4522,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9FC88B4-BAD5-4224-8F8B-E42023CF87E4}">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="3" customWidth="1"/>
@@ -3456,7 +4531,7 @@
     <col min="4" max="4" width="13.7109375" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" style="3" customWidth="1"/>
     <col min="6" max="6" width="14.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" style="3" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="3"/>
     <col min="9" max="9" width="17.85546875" style="3" customWidth="1"/>
     <col min="10" max="10" width="16" style="3" customWidth="1"/>
@@ -5169,13 +6244,125 @@
         <v>0.65141719549690702</v>
       </c>
     </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B48" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="5">
+        <v>0.90701754385964894</v>
+      </c>
+      <c r="C50" s="5">
+        <v>0.71016483516483497</v>
+      </c>
+      <c r="D50" s="5">
+        <v>0.79661016949152497</v>
+      </c>
+      <c r="E50" s="5">
+        <v>0.78190296834364603</v>
+      </c>
+      <c r="F50" s="5">
+        <v>0.57108042242079604</v>
+      </c>
+      <c r="G50" s="5">
+        <v>0.59088045011143397</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" s="5">
+        <v>0.82832080200501201</v>
+      </c>
+      <c r="C51" s="5">
+        <v>0.90796703296703296</v>
+      </c>
+      <c r="D51" s="5">
+        <v>0.86631716906946199</v>
+      </c>
+      <c r="E51" s="5">
+        <v>0.820575803077777</v>
+      </c>
+      <c r="F51" s="5">
+        <v>0.64241893076248902</v>
+      </c>
+      <c r="G51" s="5">
+        <v>0.64731008158916303</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="5">
+        <v>0.66165413533834505</v>
+      </c>
+      <c r="C52" s="5">
+        <v>0.92631578947368398</v>
+      </c>
+      <c r="D52" s="5">
+        <v>0.77192982456140302</v>
+      </c>
+      <c r="E52" s="5">
+        <v>0.73934837092731798</v>
+      </c>
+      <c r="F52" s="5">
+        <v>0.49667271627344201</v>
+      </c>
+      <c r="G52" s="5">
+        <v>0.53411494579609897</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I1:O1"/>
     <mergeCell ref="A24:G24"/>
   </mergeCells>
-  <conditionalFormatting sqref="A1:O29 A49:O1048576 A30:J48 M30:O48">
+  <conditionalFormatting sqref="A1:O29 M30:O48 A30:J48 A49:O1048576">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -5220,7 +6407,8 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -5229,8 +6417,8 @@
   <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.85546875" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="1" max="1" width="26.5703125" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">

--- a/src/results/human/human_results_for_presentation.xlsx
+++ b/src/results/human/human_results_for_presentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repos\Using-LLM-for-automated-feedback-generation-on-a-bachelor-thesis\src\results\human\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CC3066B-6B67-43D0-BE0A-7F2333FE9E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1A36541-DF51-499E-A663-440221C2A4DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Original" sheetId="1" r:id="rId1"/>
@@ -142,15 +142,6 @@
     <t>Averaged</t>
   </si>
   <si>
-    <t>human1 vs human2</t>
-  </si>
-  <si>
-    <t>human1 vs human3</t>
-  </si>
-  <si>
-    <t>human2 vs human3</t>
-  </si>
-  <si>
     <t>Pozitīva precizitāte</t>
   </si>
   <si>
@@ -167,6 +158,15 @@
   </si>
   <si>
     <t>Metjūsa korelācijas koeficients</t>
+  </si>
+  <si>
+    <t>Eksperti 1 un 2</t>
+  </si>
+  <si>
+    <t>Eksperti 1 un 3</t>
+  </si>
+  <si>
+    <t>Eksperti 2 un 3</t>
   </si>
 </sst>
 </file>
@@ -234,19 +234,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,7 +443,7 @@
             <c:numRef>
               <c:f>Transformed!$W$7:$W$26</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.71964956195244001</c:v>
@@ -608,7 +610,7 @@
             <c:numRef>
               <c:f>Transformed!$X$7:$X$26</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.86749482401656297</c:v>
@@ -775,7 +777,7 @@
             <c:numRef>
               <c:f>Transformed!$Y$7:$Y$26</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
+                <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="20"/>
                 <c:pt idx="0">
                   <c:v>0.74439324116743399</c:v>
@@ -1043,7 +1045,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1191,7 +1193,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>human1 vs human2</c:v>
+                  <c:v>Eksperti 1 un 2</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1208,9 +1210,16 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Transformed!$B$49:$G$49</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Transformed!$B$49:$G$49</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Transformed!$B$49:$F$49</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Pozitīva precizitāte</c:v>
                 </c:pt>
@@ -1225,19 +1234,23 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Koena kappa</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Metjūsa korelācijas koeficients</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Transformed!$B$50:$G$50</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Transformed!$B$50:$G$50</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Transformed!$B$50:$F$50</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.90701754385964894</c:v>
                 </c:pt>
@@ -1252,9 +1265,6 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.57108042242079604</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.59088045011143397</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1274,7 +1284,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>human1 vs human3</c:v>
+                  <c:v>Eksperti 1 un 3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1291,9 +1301,16 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Transformed!$B$49:$G$49</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Transformed!$B$49:$G$49</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Transformed!$B$49:$F$49</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Pozitīva precizitāte</c:v>
                 </c:pt>
@@ -1308,19 +1325,23 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Koena kappa</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Metjūsa korelācijas koeficients</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Transformed!$B$51:$G$51</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Transformed!$B$51:$G$51</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Transformed!$B$51:$F$51</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.82832080200501201</c:v>
                 </c:pt>
@@ -1335,9 +1356,6 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.64241893076248902</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.64731008158916303</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1357,7 +1375,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>human2 vs human3</c:v>
+                  <c:v>Eksperti 2 un 3</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1374,9 +1392,16 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Transformed!$B$49:$G$49</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Transformed!$B$49:$G$49</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Transformed!$B$49:$F$49</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>Pozitīva precizitāte</c:v>
                 </c:pt>
@@ -1391,19 +1416,23 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Koena kappa</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Metjūsa korelācijas koeficients</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Transformed!$B$52:$G$52</c:f>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>Transformed!$B$52:$G$52</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>Transformed!$B$52:$F$52</c:f>
               <c:numCache>
-                <c:formatCode>0.00</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>0.66165413533834505</c:v>
                 </c:pt>
@@ -1418,9 +1447,6 @@
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0.49667271627344201</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.53411494579609897</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1516,7 +1542,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3073,24 +3099,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="I1" s="7" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="I1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4017,15 +4043,15 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -4526,12 +4552,12 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="13.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="9" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" style="9" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="9" customWidth="1"/>
+    <col min="7" max="7" width="26.140625" style="9" customWidth="1"/>
     <col min="8" max="8" width="9.140625" style="3"/>
     <col min="9" max="9" width="17.85546875" style="3" customWidth="1"/>
     <col min="10" max="10" width="16" style="3" customWidth="1"/>
@@ -4547,66 +4573,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="I1" s="6" t="s">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="I1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5"/>
+      <c r="O1" s="5"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="7" t="s">
         <v>26</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -4614,43 +4640,43 @@
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="8">
         <v>0.97560975609756095</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="8">
         <v>0.75471698113207497</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="8">
         <v>0.85106382978723405</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="8">
         <v>0.71964956195244001</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="8">
         <v>0.46347305389221499</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="8">
         <v>0.52194031252338002</v>
       </c>
       <c r="I3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3" s="8">
         <v>0.76923076923076905</v>
       </c>
-      <c r="K3" s="5">
+      <c r="K3" s="8">
         <v>0.97560975609756095</v>
       </c>
-      <c r="L3" s="5">
+      <c r="L3" s="8">
         <v>0.86021505376343999</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="8">
         <v>0.74439324116743399</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="8">
         <v>0.50710900473933596</v>
       </c>
-      <c r="O3" s="5">
+      <c r="O3" s="8">
         <v>0.55795044436873098</v>
       </c>
     </row>
@@ -4658,43 +4684,43 @@
       <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="8">
         <v>0.30434782608695599</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="8">
         <v>0.77777777777777701</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="8">
         <v>0.4375</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="8">
         <v>0.625</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="8">
         <v>0.294981640146878</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="8">
         <v>0.35274315641259502</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="8">
         <v>0.73913043478260798</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="8">
         <v>0.73913043478260798</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="8">
         <v>0.73913043478260798</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4" s="8">
         <v>0.79639448568398696</v>
       </c>
-      <c r="N4" s="5">
+      <c r="N4" s="8">
         <v>0.59278897136797404</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="8">
         <v>0.59278897136797404</v>
       </c>
     </row>
@@ -4702,43 +4728,43 @@
       <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="8">
         <v>0.57894736842105199</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="8">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="8">
         <v>0.59459459459459396</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="8">
         <v>0.71487971487971402</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="8">
         <v>0.42992874109263601</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="8">
         <v>0.430239564006338</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="8">
         <v>0.38297872340425498</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="8">
         <v>0.94736842105263097</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="8">
         <v>0.54545454545454497</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5" s="8">
         <v>0.53079178885630496</v>
       </c>
-      <c r="N5" s="5">
+      <c r="N5" s="8">
         <v>0.21246923707957299</v>
       </c>
-      <c r="O5" s="5">
+      <c r="O5" s="8">
         <v>0.31335982576329602</v>
       </c>
     </row>
@@ -4746,43 +4772,43 @@
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="8">
         <v>0.81818181818181801</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="8">
         <v>0.219512195121951</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="8">
         <v>0.34615384615384598</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="8">
         <v>0.44939271255060698</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="8">
         <v>0.103050288540807</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="8">
         <v>0.16858537226207301</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="8">
         <v>0.19148936170212699</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="8">
         <v>0.81818181818181801</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="8">
         <v>0.31034482758620602</v>
       </c>
-      <c r="M6" s="5">
+      <c r="M6" s="8">
         <v>0.36945812807881701</v>
       </c>
-      <c r="N6" s="5">
+      <c r="N6" s="8">
         <v>4.4062733383121701E-2</v>
       </c>
-      <c r="O6" s="5">
+      <c r="O6" s="8">
         <v>8.6445888942081994E-2</v>
       </c>
       <c r="V6" s="3"/>
@@ -4800,55 +4826,55 @@
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="8">
+        <v>1</v>
+      </c>
+      <c r="C7" s="8">
         <v>0.67857142857142805</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="8">
         <v>0.80851063829787195</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="8">
         <v>0.84869976359337995</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="8">
         <v>0.70370370370370305</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="8">
         <v>0.73678839761300696</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="8">
         <v>0.81818181818181801</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="8">
         <v>0.94736842105263097</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="8">
         <v>0.87804878048780399</v>
       </c>
-      <c r="M7" s="5">
+      <c r="M7" s="8">
         <v>0.91028875805999399</v>
       </c>
-      <c r="N7" s="5">
+      <c r="N7" s="8">
         <v>0.82102908277404896</v>
       </c>
-      <c r="O7" s="5">
+      <c r="O7" s="8">
         <v>0.82580406612983304</v>
       </c>
       <c r="V7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="8">
         <v>0.71964956195244001</v>
       </c>
-      <c r="X7" s="5">
+      <c r="X7" s="8">
         <v>0.86749482401656297</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="Y7" s="8">
         <v>0.74439324116743399</v>
       </c>
     </row>
@@ -4856,55 +4882,55 @@
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="8">
         <v>0.967741935483871</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="8">
         <v>0.58823529411764697</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="8">
         <v>0.73170731707317005</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="8">
         <v>0.62672322375397604</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="8">
         <v>0.32502396931927102</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="8">
         <v>0.411628197349662</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="8">
         <v>0.54385964912280704</v>
       </c>
-      <c r="K8" s="5">
-        <v>1</v>
-      </c>
-      <c r="L8" s="5">
+      <c r="K8" s="8">
+        <v>1</v>
+      </c>
+      <c r="L8" s="8">
         <v>0.70454545454545403</v>
       </c>
-      <c r="M8" s="5">
+      <c r="M8" s="8">
         <v>0.527272727272727</v>
       </c>
-      <c r="N8" s="5">
+      <c r="N8" s="8">
         <v>0.20686367969494701</v>
       </c>
-      <c r="O8" s="5">
+      <c r="O8" s="8">
         <v>0.33965301116837798</v>
       </c>
       <c r="V8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="8">
         <v>0.625</v>
       </c>
-      <c r="X8" s="5">
+      <c r="X8" s="8">
         <v>0.58333333333333304</v>
       </c>
-      <c r="Y8" s="5">
+      <c r="Y8" s="8">
         <v>0.79639448568398696</v>
       </c>
     </row>
@@ -4912,55 +4938,55 @@
       <c r="A9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="8">
         <v>0.88461538461538403</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="8">
         <v>0.45098039215686198</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="8">
         <v>0.59740259740259705</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="8">
         <v>0.49477973007384701</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="8">
         <v>0.12829525483304</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="8">
         <v>0.18039214358783101</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="8">
         <v>0.46341463414634099</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="8">
         <v>0.73076923076922995</v>
       </c>
-      <c r="L9" s="5">
+      <c r="L9" s="8">
         <v>0.56716417910447703</v>
       </c>
-      <c r="M9" s="5">
+      <c r="M9" s="8">
         <v>0.54587717151945103</v>
       </c>
-      <c r="N9" s="5">
+      <c r="N9" s="8">
         <v>0.13914656771799599</v>
       </c>
-      <c r="O9" s="5">
+      <c r="O9" s="8">
         <v>0.15540212044034599</v>
       </c>
       <c r="V9" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="8">
         <v>0.71487971487971402</v>
       </c>
-      <c r="X9" s="5">
+      <c r="X9" s="8">
         <v>0.51550671550671501</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="Y9" s="8">
         <v>0.53079178885630496</v>
       </c>
     </row>
@@ -4968,55 +4994,55 @@
       <c r="A10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="8">
+        <v>1</v>
+      </c>
+      <c r="C10" s="8">
         <v>0.67307692307692302</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="8">
         <v>0.80459770114942497</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="8">
         <v>0.69498177740398004</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="8">
         <v>0.43568464730290402</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="8">
         <v>0.52774481414734498</v>
       </c>
       <c r="I10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="8">
         <v>0.8</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="8">
         <v>0.68571428571428505</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="8">
         <v>0.73846153846153795</v>
       </c>
-      <c r="M10" s="5">
+      <c r="M10" s="8">
         <v>0.73431013431013403</v>
       </c>
-      <c r="N10" s="5">
+      <c r="N10" s="8">
         <v>0.47184466019417398</v>
       </c>
-      <c r="O10" s="5">
+      <c r="O10" s="8">
         <v>0.477642719374823</v>
       </c>
       <c r="V10" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W10" s="8">
         <v>0.44939271255060698</v>
       </c>
-      <c r="X10" s="5">
+      <c r="X10" s="8">
         <v>0.85454545454545405</v>
       </c>
-      <c r="Y10" s="5">
+      <c r="Y10" s="8">
         <v>0.36945812807881701</v>
       </c>
     </row>
@@ -5024,55 +5050,55 @@
       <c r="A11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="8">
         <v>0.80769230769230704</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="8">
         <v>0.55263157894736803</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="8">
         <v>0.65625</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="8">
         <v>0.65625</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="8">
         <v>0.33584905660377301</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="8">
         <v>0.36032388663967602</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="8">
         <v>0.46</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="8">
         <v>0.88461538461538403</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="8">
         <v>0.60526315789473595</v>
       </c>
-      <c r="M11" s="5">
+      <c r="M11" s="8">
         <v>0.51417004048582904</v>
       </c>
-      <c r="N11" s="5">
+      <c r="N11" s="8">
         <v>0.151943462897526</v>
       </c>
-      <c r="O11" s="5">
+      <c r="O11" s="8">
         <v>0.20682401020486901</v>
       </c>
       <c r="V11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="W11" s="5">
+      <c r="W11" s="8">
         <v>0.84869976359337995</v>
       </c>
-      <c r="X11" s="5">
+      <c r="X11" s="8">
         <v>0.86871794871794805</v>
       </c>
-      <c r="Y11" s="5">
+      <c r="Y11" s="8">
         <v>0.91028875805999399</v>
       </c>
     </row>
@@ -5080,55 +5106,55 @@
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5">
-        <v>1</v>
-      </c>
-      <c r="G12" s="5">
+      <c r="B12" s="8">
+        <v>1</v>
+      </c>
+      <c r="C12" s="8">
+        <v>1</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8">
         <v>1</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J12" s="5">
-        <v>1</v>
-      </c>
-      <c r="K12" s="5">
+      <c r="J12" s="8">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8">
         <v>0.97959183673469297</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="8">
         <v>0.98969072164948402</v>
       </c>
-      <c r="M12" s="5">
+      <c r="M12" s="8">
         <v>0.97871632856667701</v>
       </c>
-      <c r="N12" s="5">
+      <c r="N12" s="8">
         <v>0.95744680851063801</v>
       </c>
-      <c r="O12" s="5">
+      <c r="O12" s="8">
         <v>0.95831484749990903</v>
       </c>
       <c r="V12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="W12" s="5">
+      <c r="W12" s="8">
         <v>0.62672322375397604</v>
       </c>
-      <c r="X12" s="5">
+      <c r="X12" s="8">
         <v>0.82222222222222197</v>
       </c>
-      <c r="Y12" s="5">
+      <c r="Y12" s="8">
         <v>0.527272727272727</v>
       </c>
     </row>
@@ -5136,55 +5162,55 @@
       <c r="A13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="5">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5">
-        <v>1</v>
-      </c>
-      <c r="G13" s="5">
+      <c r="B13" s="8">
+        <v>1</v>
+      </c>
+      <c r="C13" s="8">
+        <v>1</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
         <v>1</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="J13" s="5">
-        <v>1</v>
-      </c>
-      <c r="K13" s="5">
-        <v>1</v>
-      </c>
-      <c r="L13" s="5">
-        <v>1</v>
-      </c>
-      <c r="M13" s="5">
-        <v>1</v>
-      </c>
-      <c r="N13" s="5">
-        <v>1</v>
-      </c>
-      <c r="O13" s="5">
+      <c r="J13" s="8">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8">
+        <v>1</v>
+      </c>
+      <c r="L13" s="8">
+        <v>1</v>
+      </c>
+      <c r="M13" s="8">
+        <v>1</v>
+      </c>
+      <c r="N13" s="8">
+        <v>1</v>
+      </c>
+      <c r="O13" s="8">
         <v>1</v>
       </c>
       <c r="V13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="W13" s="5">
+      <c r="W13" s="8">
         <v>0.49477973007384701</v>
       </c>
-      <c r="X13" s="5">
+      <c r="X13" s="8">
         <v>0.76811594202898503</v>
       </c>
-      <c r="Y13" s="5">
+      <c r="Y13" s="8">
         <v>0.54587717151945103</v>
       </c>
     </row>
@@ -5192,55 +5218,55 @@
       <c r="A14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="8">
         <v>0.75</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="8">
         <v>0.22222222222222199</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="8">
         <v>0.34285714285714203</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="8">
         <v>0.54777265745007597</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="8">
         <v>0.185840707964601</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="8">
         <v>0.25112360116696097</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="8">
         <v>0.14285714285714199</v>
       </c>
-      <c r="K14" s="5">
-        <v>1</v>
-      </c>
-      <c r="L14" s="5">
+      <c r="K14" s="8">
+        <v>1</v>
+      </c>
+      <c r="L14" s="8">
         <v>0.25</v>
       </c>
-      <c r="M14" s="5">
+      <c r="M14" s="8">
         <v>0.25</v>
       </c>
-      <c r="N14" s="5">
+      <c r="N14" s="8">
         <v>0.04</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O14" s="8">
         <v>0.14285714285714199</v>
       </c>
       <c r="V14" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="5">
+      <c r="W14" s="8">
         <v>0.69498177740398004</v>
       </c>
-      <c r="X14" s="5">
+      <c r="X14" s="8">
         <v>0.55885471898197203</v>
       </c>
-      <c r="Y14" s="5">
+      <c r="Y14" s="8">
         <v>0.73431013431013403</v>
       </c>
     </row>
@@ -5248,55 +5274,55 @@
       <c r="A15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="5">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5">
+      <c r="B15" s="8">
+        <v>1</v>
+      </c>
+      <c r="C15" s="8">
         <v>0.94736842105263097</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="8">
         <v>0.97297297297297303</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="8">
         <v>0.89825119236883899</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="8">
         <v>0.797468354430379</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="8">
         <v>0.81434507104595499</v>
       </c>
       <c r="I15" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="8">
         <v>0.94642857142857095</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="8">
         <v>0.98148148148148096</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="8">
         <v>0.96363636363636296</v>
       </c>
-      <c r="M15" s="5">
+      <c r="M15" s="8">
         <v>0.87070707070706999</v>
       </c>
-      <c r="N15" s="5">
+      <c r="N15" s="8">
         <v>0.74193548387096697</v>
       </c>
-      <c r="O15" s="5">
+      <c r="O15" s="8">
         <v>0.748190055927208</v>
       </c>
       <c r="V15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="W15" s="5">
+      <c r="W15" s="8">
         <v>0.65625</v>
       </c>
-      <c r="X15" s="5">
+      <c r="X15" s="8">
         <v>0.67272727272727195</v>
       </c>
-      <c r="Y15" s="5">
+      <c r="Y15" s="8">
         <v>0.51417004048582904</v>
       </c>
     </row>
@@ -5304,55 +5330,55 @@
       <c r="A16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="8">
         <v>0.98214285714285698</v>
       </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="8">
+        <v>1</v>
+      </c>
+      <c r="D16" s="8">
         <v>0.99099099099099097</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="8">
         <v>0.96608373078961296</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="8">
         <v>0.93220338983050799</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="8">
         <v>0.93435318430231296</v>
       </c>
       <c r="I16" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="5">
-        <v>1</v>
-      </c>
-      <c r="K16" s="5">
+      <c r="J16" s="8">
+        <v>1</v>
+      </c>
+      <c r="K16" s="8">
         <v>0.98214285714285698</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="8">
         <v>0.99099099099099097</v>
       </c>
-      <c r="M16" s="5">
+      <c r="M16" s="8">
         <v>0.96608373078961296</v>
       </c>
-      <c r="N16" s="5">
+      <c r="N16" s="8">
         <v>0.93220338983050799</v>
       </c>
-      <c r="O16" s="5">
+      <c r="O16" s="8">
         <v>0.93435318430231296</v>
       </c>
       <c r="V16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="W16" s="5">
-        <v>1</v>
-      </c>
-      <c r="X16" s="5">
+      <c r="W16" s="8">
+        <v>1</v>
+      </c>
+      <c r="X16" s="8">
         <v>0.97871632856667701</v>
       </c>
-      <c r="Y16" s="5">
+      <c r="Y16" s="8">
         <v>0.97871632856667701</v>
       </c>
     </row>
@@ -5360,55 +5386,55 @@
       <c r="A17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="8">
         <v>0.95121951219512102</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="8">
         <v>0.73584905660377298</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="8">
         <v>0.82978723404255295</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="8">
         <v>0.67959949937421704</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="8">
         <v>0.38682634730538901</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="8">
         <v>0.43562460192519797</v>
       </c>
       <c r="I17" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="8">
         <v>0.79166666666666596</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="8">
         <v>0.92682926829268297</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="8">
         <v>0.85393258426966201</v>
       </c>
-      <c r="M17" s="5">
+      <c r="M17" s="8">
         <v>0.76029962546816399</v>
       </c>
-      <c r="N17" s="5">
+      <c r="N17" s="8">
         <v>0.527272727272727</v>
       </c>
-      <c r="O17" s="5">
+      <c r="O17" s="8">
         <v>0.54523223508263496</v>
       </c>
       <c r="V17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="W17" s="5">
-        <v>1</v>
-      </c>
-      <c r="X17" s="5">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="5">
+      <c r="W17" s="8">
+        <v>1</v>
+      </c>
+      <c r="X17" s="8">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="8">
         <v>1</v>
       </c>
     </row>
@@ -5416,55 +5442,55 @@
       <c r="A18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="8">
         <v>0.77777777777777701</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="8">
         <v>0.65116279069767402</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="8">
         <v>0.70886075949367</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="8">
         <v>0.619736502195815</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="8">
         <v>0.24897959183673399</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="8">
         <v>0.255750025170776</v>
       </c>
       <c r="I18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J18" s="5">
+      <c r="J18" s="8">
         <v>0.61016949152542299</v>
       </c>
-      <c r="K18" s="5">
-        <v>1</v>
-      </c>
-      <c r="L18" s="5">
+      <c r="K18" s="8">
+        <v>1</v>
+      </c>
+      <c r="L18" s="8">
         <v>0.75789473684210495</v>
       </c>
-      <c r="M18" s="5">
+      <c r="M18" s="8">
         <v>0.53046251993620397</v>
       </c>
-      <c r="N18" s="5">
+      <c r="N18" s="8">
         <v>0.19650655021833999</v>
       </c>
-      <c r="O18" s="5">
+      <c r="O18" s="8">
         <v>0.33008913610174601</v>
       </c>
       <c r="V18" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="W18" s="5">
+      <c r="W18" s="8">
         <v>0.54777265745007597</v>
       </c>
-      <c r="X18" s="5">
+      <c r="X18" s="8">
         <v>0.50307898259705397</v>
       </c>
-      <c r="Y18" s="5">
+      <c r="Y18" s="8">
         <v>0.25</v>
       </c>
     </row>
@@ -5472,55 +5498,55 @@
       <c r="A19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5">
+      <c r="B19" s="8">
+        <v>1</v>
+      </c>
+      <c r="C19" s="8">
         <v>0.77777777777777701</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="8">
         <v>0.875</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="8">
         <v>0.91666666666666596</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="8">
         <v>0.83419689119170903</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="8">
         <v>0.84590516936330096</v>
       </c>
       <c r="I19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="8">
         <v>0.73684210526315697</v>
       </c>
-      <c r="K19" s="5">
-        <v>1</v>
-      </c>
-      <c r="L19" s="5">
+      <c r="K19" s="8">
+        <v>1</v>
+      </c>
+      <c r="L19" s="8">
         <v>0.84848484848484795</v>
       </c>
-      <c r="M19" s="5">
+      <c r="M19" s="8">
         <v>0.89792663476874002</v>
       </c>
-      <c r="N19" s="5">
+      <c r="N19" s="8">
         <v>0.797468354430379</v>
       </c>
-      <c r="O19" s="5">
+      <c r="O19" s="8">
         <v>0.81434507104595499</v>
       </c>
       <c r="V19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="W19" s="5">
+      <c r="W19" s="8">
         <v>0.89825119236883899</v>
       </c>
-      <c r="X19" s="5">
+      <c r="X19" s="8">
         <v>0.96224188790560405</v>
       </c>
-      <c r="Y19" s="5">
+      <c r="Y19" s="8">
         <v>0.87070707070706999</v>
       </c>
     </row>
@@ -5528,55 +5554,55 @@
       <c r="A20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="8">
         <v>0.9</v>
       </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="8">
+        <v>1</v>
+      </c>
+      <c r="D20" s="8">
         <v>0.94736842105263097</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="8">
         <v>0.96257309941520397</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="8">
         <v>0.92523364485981296</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="8">
         <v>0.92783056924062901</v>
       </c>
       <c r="I20" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="8">
         <v>0.94736842105263097</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="8">
         <v>0.9</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="8">
         <v>0.92307692307692302</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M20" s="8">
         <v>0.94468452895419097</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N20" s="8">
         <v>0.88940092165898599</v>
       </c>
-      <c r="O20" s="5">
+      <c r="O20" s="8">
         <v>0.89000594350768203</v>
       </c>
       <c r="V20" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="W20" s="5">
+      <c r="W20" s="8">
         <v>0.96608373078961296</v>
       </c>
-      <c r="X20" s="5">
+      <c r="X20" s="8">
         <v>0.93535353535353505</v>
       </c>
-      <c r="Y20" s="5">
+      <c r="Y20" s="8">
         <v>0.96608373078961296</v>
       </c>
     </row>
@@ -5584,55 +5610,55 @@
       <c r="A21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="8">
         <v>0.8</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="8">
         <v>0.5</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="8">
         <v>0.61538461538461497</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="8">
         <v>0.75867269984916996</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="8">
         <v>0.52380952380952295</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="8">
         <v>0.54659439449994796</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="8">
         <v>0.44444444444444398</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="8">
         <v>0.8</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="8">
         <v>0.57142857142857095</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="8">
         <v>0.72571428571428498</v>
       </c>
-      <c r="N21" s="5">
+      <c r="N21" s="8">
         <v>0.463687150837988</v>
       </c>
-      <c r="O21" s="5">
+      <c r="O21" s="8">
         <v>0.49650775412030801</v>
       </c>
       <c r="V21" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="W21" s="5">
+      <c r="W21" s="8">
         <v>0.67959949937421704</v>
       </c>
-      <c r="X21" s="5">
+      <c r="X21" s="8">
         <v>0.741840850751741</v>
       </c>
-      <c r="Y21" s="5">
+      <c r="Y21" s="8">
         <v>0.76029962546816399</v>
       </c>
     </row>
@@ -5640,55 +5666,55 @@
       <c r="A22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="8">
         <v>0.86833034440498402</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="8">
         <v>0.69163126054564295</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="8">
         <v>0.742684350592279</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="8">
         <v>0.74630065959566005</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="8">
         <v>0.52918677929809899</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="8">
         <v>0.56325855059247298</v>
       </c>
       <c r="I22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="8">
         <v>0.67305590704256602</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="8">
         <v>0.91046332610094005</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="8">
         <v>0.74198756381367104</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="8">
         <v>0.71566058949155897</v>
       </c>
-      <c r="N22" s="5">
+      <c r="N22" s="8">
         <v>0.51016730455153803</v>
       </c>
-      <c r="O22" s="5">
+      <c r="O22" s="8">
         <v>0.54819823306343296</v>
       </c>
       <c r="V22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="W22" s="5">
+      <c r="W22" s="8">
         <v>0.619736502195815</v>
       </c>
-      <c r="X22" s="5">
+      <c r="X22" s="8">
         <v>0.61387631975867196</v>
       </c>
-      <c r="Y22" s="5">
+      <c r="Y22" s="8">
         <v>0.53046251993620397</v>
       </c>
     </row>
@@ -5696,36 +5722,36 @@
       <c r="V23" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="W23" s="5">
+      <c r="W23" s="8">
         <v>0.91666666666666596</v>
       </c>
-      <c r="X23" s="5">
+      <c r="X23" s="8">
         <v>0.942975942975943</v>
       </c>
-      <c r="Y23" s="5">
+      <c r="Y23" s="8">
         <v>0.89792663476874002</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
       <c r="V24" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="W24" s="5">
+      <c r="W24" s="8">
         <v>0.96257309941520397</v>
       </c>
-      <c r="X24" s="5">
+      <c r="X24" s="8">
         <v>0.942975942975943</v>
       </c>
-      <c r="Y24" s="5">
+      <c r="Y24" s="8">
         <v>0.94468452895419097</v>
       </c>
     </row>
@@ -5733,34 +5759,34 @@
       <c r="A25" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="7" t="s">
         <v>26</v>
       </c>
       <c r="V25" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="W25" s="5">
+      <c r="W25" s="8">
         <v>0.75867269984916996</v>
       </c>
-      <c r="X25" s="5">
+      <c r="X25" s="8">
         <v>0.91989987484355396</v>
       </c>
-      <c r="Y25" s="5">
+      <c r="Y25" s="8">
         <v>0.72571428571428498</v>
       </c>
     </row>
@@ -5768,35 +5794,35 @@
       <c r="A26" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="8">
         <v>0.96153846153846101</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="8">
         <v>0.94339622641509402</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="8">
         <v>0.952380952380952</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="8">
         <v>0.86749482401656297</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="8">
         <v>0.73509933774834402</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="8">
         <v>0.73613318780907899</v>
       </c>
       <c r="O26"/>
       <c r="V26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="W26" s="5">
+      <c r="W26" s="8">
         <v>0.74630065959566005</v>
       </c>
-      <c r="X26" s="5">
+      <c r="X26" s="8">
         <v>0.79223568935837796</v>
       </c>
-      <c r="Y26" s="5">
+      <c r="Y26" s="8">
         <v>0.71566058949155897</v>
       </c>
     </row>
@@ -5804,22 +5830,22 @@
       <c r="A27" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="8">
         <v>0.26086956521739102</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="8">
         <v>0.66666666666666596</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="8">
         <v>0.375</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="8">
         <v>0.58333333333333304</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="8">
         <v>0.21664626682986499</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="8">
         <v>0.25906862524908397</v>
       </c>
       <c r="O27"/>
@@ -5828,22 +5854,22 @@
       <c r="A28" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="8">
         <v>0.36170212765957399</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="8">
         <v>0.94444444444444398</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="8">
         <v>0.52307692307692299</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="8">
         <v>0.51550671550671501</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="8">
         <v>0.19611021069692</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="8">
         <v>0.29752729094969899</v>
       </c>
       <c r="O28"/>
@@ -5852,22 +5878,22 @@
       <c r="A29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="8">
         <v>0.85106382978723405</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="8">
         <v>0.97560975609756095</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="8">
         <v>0.90909090909090895</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="8">
         <v>0.85454545454545405</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="8">
         <v>0.71203599550056196</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="8">
         <v>0.72924670246921097</v>
       </c>
       <c r="O29"/>
@@ -5876,22 +5902,22 @@
       <c r="A30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="8">
         <v>0.95454545454545403</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="8">
         <v>0.75</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="8">
         <v>0.84</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="8">
         <v>0.86871794871794805</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="8">
         <v>0.73983739837398299</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="8">
         <v>0.75433650914135697</v>
       </c>
       <c r="O30"/>
@@ -5900,22 +5926,22 @@
       <c r="A31" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="8">
         <v>0.89473684210526305</v>
       </c>
-      <c r="C31" s="5">
-        <v>1</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="8">
+        <v>1</v>
+      </c>
+      <c r="D31" s="8">
         <v>0.94444444444444398</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="8">
         <v>0.82222222222222197</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="8">
         <v>0.65027322404371501</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="8">
         <v>0.69410473022319796</v>
       </c>
       <c r="O31"/>
@@ -5924,22 +5950,22 @@
       <c r="A32" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="8">
         <v>0.97560975609756095</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="8">
         <v>0.78431372549019596</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="8">
         <v>0.86956521739130399</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="8">
         <v>0.76811594202898503</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="8">
         <v>0.54982415005861596</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="8">
         <v>0.59314412363964997</v>
       </c>
       <c r="O32"/>
@@ -5948,22 +5974,22 @@
       <c r="A33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="8">
         <v>0.93333333333333302</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="8">
         <v>0.53846153846153799</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="8">
         <v>0.68292682926829196</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="8">
         <v>0.55885471898197203</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="8">
         <v>0.21804511278195399</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="8">
         <v>0.29080080483815601</v>
       </c>
       <c r="O33"/>
@@ -5972,22 +5998,22 @@
       <c r="A34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="8">
         <v>0.7</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="8">
         <v>0.92105263157894701</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="8">
         <v>0.79545454545454497</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="8">
         <v>0.67272727272727195</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="8">
         <v>0.37117903930131002</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="8">
         <v>0.40883815970729898</v>
       </c>
     </row>
@@ -5995,22 +6021,22 @@
       <c r="A35" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="5">
-        <v>1</v>
-      </c>
-      <c r="C35" s="5">
+      <c r="B35" s="8">
+        <v>1</v>
+      </c>
+      <c r="C35" s="8">
         <v>0.97959183673469297</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="8">
         <v>0.98969072164948402</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="8">
         <v>0.97871632856667701</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="8">
         <v>0.95744680851063801</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="8">
         <v>0.95831484749990903</v>
       </c>
     </row>
@@ -6018,22 +6044,22 @@
       <c r="A36" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B36" s="5">
-        <v>1</v>
-      </c>
-      <c r="C36" s="5">
-        <v>1</v>
-      </c>
-      <c r="D36" s="5">
-        <v>1</v>
-      </c>
-      <c r="E36" s="5">
-        <v>1</v>
-      </c>
-      <c r="F36" s="5">
-        <v>1</v>
-      </c>
-      <c r="G36" s="5">
+      <c r="B36" s="8">
+        <v>1</v>
+      </c>
+      <c r="C36" s="8">
+        <v>1</v>
+      </c>
+      <c r="D36" s="8">
+        <v>1</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1</v>
+      </c>
+      <c r="F36" s="8">
+        <v>1</v>
+      </c>
+      <c r="G36" s="8">
         <v>1</v>
       </c>
     </row>
@@ -6041,22 +6067,22 @@
       <c r="A37" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="8">
         <v>0.48214285714285698</v>
       </c>
-      <c r="C37" s="5">
-        <v>1</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C37" s="8">
+        <v>1</v>
+      </c>
+      <c r="D37" s="8">
         <v>0.65060240963855398</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="8">
         <v>0.50307898259705397</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="8">
         <v>0.188811188811188</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="8">
         <v>0.32287320150037802</v>
       </c>
     </row>
@@ -6064,22 +6090,22 @@
       <c r="A38" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B38" s="5">
-        <v>1</v>
-      </c>
-      <c r="C38" s="5">
+      <c r="B38" s="8">
+        <v>1</v>
+      </c>
+      <c r="C38" s="8">
         <v>0.98245614035087703</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="8">
         <v>0.99115044247787598</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="8">
         <v>0.96224188790560405</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="8">
         <v>0.92452830188679203</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="8">
         <v>0.92717264994552995</v>
       </c>
     </row>
@@ -6087,22 +6113,22 @@
       <c r="A39" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="8">
         <v>0.98181818181818103</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="8">
         <v>0.98181818181818103</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="8">
         <v>0.98181818181818103</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="8">
         <v>0.93535353535353505</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="8">
         <v>0.87070707070706999</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="8">
         <v>0.87070707070706999</v>
       </c>
     </row>
@@ -6110,22 +6136,22 @@
       <c r="A40" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="8">
         <v>0.9375</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="8">
         <v>0.84905660377358405</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="8">
         <v>0.89108910891089099</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="8">
         <v>0.741840850751741</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="8">
         <v>0.48837209302325502</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="8">
         <v>0.50213950485175096</v>
       </c>
     </row>
@@ -6133,22 +6159,22 @@
       <c r="A41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="8">
         <v>0.72881355932203296</v>
       </c>
-      <c r="C41" s="5">
-        <v>1</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C41" s="8">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8">
         <v>0.84313725490196001</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="8">
         <v>0.61387631975867196</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="8">
         <v>0.29573590096286101</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="8">
         <v>0.41656576663693501</v>
       </c>
     </row>
@@ -6156,22 +6182,22 @@
       <c r="A42" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="8">
         <v>0.89473684210526305</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="8">
         <v>0.94444444444444398</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="8">
         <v>0.91891891891891897</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="8">
         <v>0.942975942975943</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="8">
         <v>0.88598574821852705</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="8">
         <v>0.88662628383626696</v>
       </c>
     </row>
@@ -6179,22 +6205,22 @@
       <c r="A43" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="8">
         <v>0.89473684210526305</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="8">
         <v>0.94444444444444398</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="8">
         <v>0.91891891891891897</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="8">
         <v>0.942975942975943</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="8">
         <v>0.88598574821852705</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="8">
         <v>0.88662628383626696</v>
       </c>
     </row>
@@ -6202,22 +6228,22 @@
       <c r="A44" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="8">
         <v>0.83333333333333304</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="8">
         <v>0.9375</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="8">
         <v>0.88235294117647001</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="8">
         <v>0.91989987484355396</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="8">
         <v>0.84</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="8">
         <v>0.84270097160038404</v>
       </c>
     </row>
@@ -6225,42 +6251,42 @@
       <c r="A45" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="8">
         <v>0.82349899926901005</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="8">
         <v>0.90227666530108797</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="8">
         <v>0.83997993260624304</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="8">
         <v>0.79223568935837796</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="8">
         <v>0.61719071556179605</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="8">
         <v>0.65141719549690702</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -6268,91 +6294,91 @@
       <c r="A49" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E49" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="F49" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="G49" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B50" s="5">
+        <v>40</v>
+      </c>
+      <c r="B50" s="8">
         <v>0.90701754385964894</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="8">
         <v>0.71016483516483497</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="8">
         <v>0.79661016949152497</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="8">
         <v>0.78190296834364603</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="8">
         <v>0.57108042242079604</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="8">
         <v>0.59088045011143397</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B51" s="5">
+        <v>41</v>
+      </c>
+      <c r="B51" s="8">
         <v>0.82832080200501201</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="8">
         <v>0.90796703296703296</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="8">
         <v>0.86631716906946199</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="8">
         <v>0.820575803077777</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="8">
         <v>0.64241893076248902</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="8">
         <v>0.64731008158916303</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B52" s="5">
+        <v>42</v>
+      </c>
+      <c r="B52" s="8">
         <v>0.66165413533834505</v>
       </c>
-      <c r="C52" s="5">
+      <c r="C52" s="8">
         <v>0.92631578947368398</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="8">
         <v>0.77192982456140302</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E52" s="8">
         <v>0.73934837092731798</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="8">
         <v>0.49667271627344201</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="8">
         <v>0.53411494579609897</v>
       </c>
     </row>
